--- a/Assets/Excal/RoleInfo.xlsx
+++ b/Assets/Excal/RoleInfo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9767"/>
+    <workbookView windowWidth="22185" windowHeight="9720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1035,9 +1035,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
-    <col min="5" max="5" width="10.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="10.775" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1071,7 +1071,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -1094,7 +1094,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -1117,7 +1117,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -1140,7 +1140,7 @@
         <v>16</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -1163,7 +1163,7 @@
         <v>19</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
@@ -1186,7 +1186,7 @@
         <v>22</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
         <v>23</v>
@@ -1212,7 +1212,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1224,7 +1224,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Assets/Excal/RoleInfo.xlsx
+++ b/Assets/Excal/RoleInfo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22185" windowHeight="9720"/>
+    <workbookView windowWidth="24750" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>id</t>
   </si>
@@ -67,43 +67,28 @@
     <t>角色2</t>
   </si>
   <si>
-    <t>Eff/2</t>
-  </si>
-  <si>
     <t>Role/3</t>
   </si>
   <si>
     <t>角色3</t>
   </si>
   <si>
-    <t>Eff/3</t>
-  </si>
-  <si>
     <t>Role/4</t>
   </si>
   <si>
     <t>角色4</t>
   </si>
   <si>
-    <t>Eff/4</t>
-  </si>
-  <si>
     <t>Role/5</t>
   </si>
   <si>
     <t>角色5</t>
   </si>
   <si>
-    <t>Eff/5</t>
-  </si>
-  <si>
     <t>Role/6</t>
   </si>
   <si>
     <t>角色6</t>
-  </si>
-  <si>
-    <t>Eff/6</t>
   </si>
 </sst>
 </file>
@@ -1106,7 +1091,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1114,13 +1099,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4">
         <v>200</v>
@@ -1129,7 +1114,7 @@
         <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1137,13 +1122,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5">
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E5">
         <v>300</v>
@@ -1152,7 +1137,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1160,13 +1145,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C6">
         <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E6">
         <v>400</v>
@@ -1175,7 +1160,7 @@
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1183,13 +1168,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C7">
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>700</v>
@@ -1198,7 +1183,7 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
